--- a/Entregable Planeacion 2027.xlsx
+++ b/Entregable Planeacion 2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1130613425\Documents\ACH\ACH-RADAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\1130613425\Documents\ACH\ACH-RADAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E79F6947-D4A0-4AD9-B1B6-CCEFB3C0DEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E94484-20FA-4069-98D0-296206EE68D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="870" firstSheet="1" activeTab="6" xr2:uid="{FB206A62-7075-4317-AE74-35A363C55576}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="870" firstSheet="1" activeTab="2" xr2:uid="{FB206A62-7075-4317-AE74-35A363C55576}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja6" sheetId="7" state="hidden" r:id="rId1"/>
@@ -2892,7 +2892,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3012,6 +3012,13 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3222,7 +3229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3411,6 +3418,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3426,10 +3434,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3750,24 +3754,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA04BAA6-44CF-4914-9D23-9F3862DED549}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3783,18 +3787,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" style="64" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" style="64" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
-    <col min="16383" max="16383" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16384" max="16384" width="8.85546875" customWidth="1"/>
+    <col min="16383" max="16383" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="16384" max="16384" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>641</v>
       </c>
@@ -3814,7 +3818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="60">
         <v>0</v>
       </c>
@@ -3835,7 +3839,7 @@
       </c>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.3">
       <c r="A3" s="60">
         <v>0</v>
       </c>
@@ -3856,7 +3860,7 @@
       </c>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A4" s="60">
         <v>1</v>
       </c>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A5" s="60">
         <v>1</v>
       </c>
@@ -3898,7 +3902,7 @@
       </c>
       <c r="G5" s="6"/>
     </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3918,7 +3922,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3938,7 +3942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3958,7 +3962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -3978,7 +3982,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -3998,7 +4002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4018,7 +4022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4038,7 +4042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4058,7 +4062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="48" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4078,7 +4082,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4098,7 +4102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4118,7 +4122,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -4138,7 +4142,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4158,7 +4162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4178,7 +4182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4198,7 +4202,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4218,7 +4222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4238,7 +4242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4258,7 +4262,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2</v>
       </c>
@@ -4278,7 +4282,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -4298,7 +4302,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4318,7 +4322,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4338,7 +4342,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4358,7 +4362,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
@@ -4378,7 +4382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2</v>
       </c>
@@ -4398,7 +4402,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="72" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2</v>
       </c>
@@ -4418,7 +4422,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4438,7 +4442,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4458,7 +4462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>4</v>
       </c>
@@ -4478,7 +4482,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="48" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="48" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>4</v>
       </c>
@@ -4513,18 +4517,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3AF295-C520-4CBD-81B8-D7C2E0918AC5}">
   <dimension ref="A1:H127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="49.28515625" customWidth="1"/>
-    <col min="3" max="3" width="51.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36.28515625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" customWidth="1"/>
+    <col min="3" max="3" width="51.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" style="35" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>641</v>
       </c>
@@ -4546,7 +4550,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="66">
+        <v>0</v>
+      </c>
       <c r="B2" s="23" t="s">
         <v>85</v>
       </c>
@@ -4563,7 +4570,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="66">
+        <v>0</v>
+      </c>
       <c r="B3" s="23" t="s">
         <v>89</v>
       </c>
@@ -4580,7 +4590,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="66">
+        <v>0</v>
+      </c>
       <c r="B4" s="23" t="s">
         <v>93</v>
       </c>
@@ -4597,7 +4610,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="66">
+        <v>0</v>
+      </c>
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -4614,7 +4630,10 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="66">
+        <v>0</v>
+      </c>
       <c r="B6" s="23" t="s">
         <v>101</v>
       </c>
@@ -4631,7 +4650,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="66">
+        <v>0</v>
+      </c>
       <c r="B7" s="23" t="s">
         <v>105</v>
       </c>
@@ -4648,7 +4670,10 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="66">
+        <v>1</v>
+      </c>
       <c r="B8" s="23" t="s">
         <v>85</v>
       </c>
@@ -4665,7 +4690,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="66">
+        <v>1</v>
+      </c>
       <c r="B9" s="23" t="s">
         <v>85</v>
       </c>
@@ -4682,7 +4710,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="66">
+        <v>1</v>
+      </c>
       <c r="B10" s="23" t="s">
         <v>112</v>
       </c>
@@ -4699,7 +4730,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="66">
+        <v>1</v>
+      </c>
       <c r="B11" s="23" t="s">
         <v>89</v>
       </c>
@@ -4716,7 +4750,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="66">
+        <v>1</v>
+      </c>
       <c r="B12" s="23" t="s">
         <v>117</v>
       </c>
@@ -4733,7 +4770,10 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="66">
+        <v>1</v>
+      </c>
       <c r="B13" s="23" t="s">
         <v>121</v>
       </c>
@@ -4750,7 +4790,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="66">
+        <v>1</v>
+      </c>
       <c r="B14" s="23" t="s">
         <v>125</v>
       </c>
@@ -4767,7 +4810,10 @@
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="66">
+        <v>1</v>
+      </c>
       <c r="B15" s="23" t="s">
         <v>129</v>
       </c>
@@ -4784,7 +4830,10 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="66">
+        <v>1</v>
+      </c>
       <c r="B16" s="23" t="s">
         <v>101</v>
       </c>
@@ -4801,7 +4850,10 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="66">
+        <v>2</v>
+      </c>
       <c r="B17" s="23" t="s">
         <v>134</v>
       </c>
@@ -4818,7 +4870,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="66">
+        <v>2</v>
+      </c>
       <c r="B18" s="23" t="s">
         <v>138</v>
       </c>
@@ -4835,7 +4890,10 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="66">
+        <v>2</v>
+      </c>
       <c r="B19" s="23" t="s">
         <v>142</v>
       </c>
@@ -4852,7 +4910,10 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="66">
+        <v>2</v>
+      </c>
       <c r="B20" s="23" t="s">
         <v>93</v>
       </c>
@@ -4869,7 +4930,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="66">
+        <v>2</v>
+      </c>
       <c r="B21" s="23" t="s">
         <v>147</v>
       </c>
@@ -4886,7 +4950,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="66">
+        <v>2</v>
+      </c>
       <c r="B22" s="23" t="s">
         <v>151</v>
       </c>
@@ -4903,7 +4970,10 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="66">
+        <v>2</v>
+      </c>
       <c r="B23" s="23" t="s">
         <v>155</v>
       </c>
@@ -4920,7 +4990,10 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="66">
+        <v>2</v>
+      </c>
       <c r="B24" s="23" t="s">
         <v>159</v>
       </c>
@@ -4937,7 +5010,10 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="135" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="66">
+        <v>2</v>
+      </c>
       <c r="B25" s="23" t="s">
         <v>163</v>
       </c>
@@ -4954,7 +5030,10 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="135" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="66">
+        <v>2</v>
+      </c>
       <c r="B26" s="23" t="s">
         <v>167</v>
       </c>
@@ -4971,7 +5050,10 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="66">
+        <v>2</v>
+      </c>
       <c r="B27" s="23" t="s">
         <v>171</v>
       </c>
@@ -4988,7 +5070,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="150" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="66">
+        <v>2</v>
+      </c>
       <c r="B28" s="23" t="s">
         <v>175</v>
       </c>
@@ -5005,7 +5090,10 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="66">
+        <v>3</v>
+      </c>
       <c r="B29" s="23" t="s">
         <v>134</v>
       </c>
@@ -5022,7 +5110,10 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="66">
+        <v>3</v>
+      </c>
       <c r="B30" s="23" t="s">
         <v>93</v>
       </c>
@@ -5039,7 +5130,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="66">
+        <v>3</v>
+      </c>
       <c r="B31" s="23" t="s">
         <v>181</v>
       </c>
@@ -5056,7 +5150,10 @@
         <v>184</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="66">
+        <v>3</v>
+      </c>
       <c r="B32" s="23" t="s">
         <v>185</v>
       </c>
@@ -5073,7 +5170,10 @@
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="66">
+        <v>3</v>
+      </c>
       <c r="B33" s="23" t="s">
         <v>189</v>
       </c>
@@ -5090,7 +5190,10 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="66">
+        <v>3</v>
+      </c>
       <c r="B34" s="23" t="s">
         <v>171</v>
       </c>
@@ -5107,7 +5210,10 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="66">
+        <v>3</v>
+      </c>
       <c r="B35" s="23" t="s">
         <v>194</v>
       </c>
@@ -5124,7 +5230,10 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="66">
+        <v>3</v>
+      </c>
       <c r="B36" s="23" t="s">
         <v>198</v>
       </c>
@@ -5141,7 +5250,10 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="66">
+        <v>4</v>
+      </c>
       <c r="B37" s="23" t="s">
         <v>85</v>
       </c>
@@ -5158,7 +5270,10 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="66">
+        <v>4</v>
+      </c>
       <c r="B38" s="23" t="s">
         <v>138</v>
       </c>
@@ -5175,7 +5290,10 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="66">
+        <v>4</v>
+      </c>
       <c r="B39" s="23" t="s">
         <v>93</v>
       </c>
@@ -5192,7 +5310,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="135" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="66">
+        <v>4</v>
+      </c>
       <c r="B40" s="23" t="s">
         <v>205</v>
       </c>
@@ -5209,7 +5330,10 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="66">
+        <v>4</v>
+      </c>
       <c r="B41" s="23" t="s">
         <v>93</v>
       </c>
@@ -5226,7 +5350,10 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="120" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="66">
+        <v>4</v>
+      </c>
       <c r="B42" s="23" t="s">
         <v>125</v>
       </c>
@@ -5243,7 +5370,10 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="2:6" ht="150" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="66">
+        <v>4</v>
+      </c>
       <c r="B43" s="23" t="s">
         <v>175</v>
       </c>
@@ -5260,256 +5390,256 @@
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F44" s="32"/>
     </row>
-    <row r="45" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F45" s="33"/>
     </row>
-    <row r="46" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F46" s="34"/>
     </row>
-    <row r="47" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F47" s="32"/>
     </row>
-    <row r="48" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F48" s="33"/>
     </row>
-    <row r="49" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F49" s="34"/>
     </row>
-    <row r="50" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F50" s="32"/>
     </row>
-    <row r="51" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F51" s="33"/>
     </row>
-    <row r="52" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F52" s="34"/>
     </row>
-    <row r="53" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F53" s="32"/>
     </row>
-    <row r="54" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F54" s="33"/>
     </row>
-    <row r="55" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F55" s="34"/>
     </row>
-    <row r="56" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F56" s="32"/>
     </row>
-    <row r="57" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F57" s="33"/>
     </row>
-    <row r="58" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F58" s="34"/>
     </row>
-    <row r="59" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F59" s="32"/>
     </row>
-    <row r="60" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F60" s="33"/>
     </row>
-    <row r="61" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F61" s="34"/>
     </row>
-    <row r="62" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F62" s="32"/>
     </row>
-    <row r="63" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F63" s="33"/>
     </row>
-    <row r="64" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F64" s="34"/>
     </row>
-    <row r="65" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F65" s="32"/>
     </row>
-    <row r="66" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F66" s="33"/>
     </row>
-    <row r="67" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F67" s="34"/>
     </row>
-    <row r="68" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F68" s="32"/>
     </row>
-    <row r="69" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F69" s="33"/>
     </row>
-    <row r="70" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F70" s="34"/>
     </row>
-    <row r="71" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F71" s="32"/>
     </row>
-    <row r="72" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F72" s="33"/>
     </row>
-    <row r="73" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F73" s="34"/>
     </row>
-    <row r="74" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F74" s="32"/>
     </row>
-    <row r="75" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F75" s="33"/>
     </row>
-    <row r="76" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F76" s="34"/>
     </row>
-    <row r="77" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F77" s="32"/>
     </row>
-    <row r="78" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F78" s="33"/>
     </row>
-    <row r="79" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F79" s="34"/>
     </row>
-    <row r="80" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F80" s="32"/>
     </row>
-    <row r="81" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F81" s="33"/>
     </row>
-    <row r="82" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F82" s="34"/>
     </row>
-    <row r="83" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F83" s="32"/>
     </row>
-    <row r="84" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F84" s="33"/>
     </row>
-    <row r="85" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F85" s="34"/>
     </row>
-    <row r="86" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F86" s="32"/>
     </row>
-    <row r="87" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F87" s="33"/>
     </row>
-    <row r="88" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F88" s="34"/>
     </row>
-    <row r="89" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F89" s="32"/>
     </row>
-    <row r="90" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F90" s="33"/>
     </row>
-    <row r="91" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F91" s="34"/>
     </row>
-    <row r="92" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F92" s="32"/>
     </row>
-    <row r="93" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F93" s="33"/>
     </row>
-    <row r="94" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F95" s="32"/>
     </row>
-    <row r="96" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F96" s="33"/>
     </row>
-    <row r="97" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F97" s="34"/>
     </row>
-    <row r="98" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F98" s="32"/>
     </row>
-    <row r="99" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F99" s="33"/>
     </row>
-    <row r="100" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F100" s="34"/>
     </row>
-    <row r="101" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F101" s="32"/>
     </row>
-    <row r="102" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F102" s="33"/>
     </row>
-    <row r="103" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F103" s="34"/>
     </row>
-    <row r="104" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F104" s="32"/>
     </row>
-    <row r="105" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F105" s="33"/>
     </row>
-    <row r="106" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F106" s="34"/>
     </row>
-    <row r="107" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F107" s="32"/>
     </row>
-    <row r="108" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F108" s="33"/>
     </row>
-    <row r="109" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F109" s="34"/>
     </row>
-    <row r="110" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F110" s="32"/>
     </row>
-    <row r="111" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F111" s="33"/>
     </row>
-    <row r="112" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F112" s="34"/>
     </row>
-    <row r="113" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F113" s="32"/>
     </row>
-    <row r="114" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F114" s="33"/>
     </row>
-    <row r="115" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F115" s="34"/>
     </row>
-    <row r="116" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F116" s="32"/>
     </row>
-    <row r="117" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F117" s="33"/>
     </row>
-    <row r="118" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F118" s="34"/>
     </row>
-    <row r="119" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F119" s="32"/>
     </row>
-    <row r="120" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F120" s="33"/>
     </row>
-    <row r="121" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F121" s="34"/>
     </row>
-    <row r="122" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F122" s="32"/>
     </row>
-    <row r="123" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F123" s="33"/>
     </row>
-    <row r="124" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F124" s="34"/>
     </row>
-    <row r="125" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F125" s="32"/>
     </row>
-    <row r="126" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F126" s="33"/>
     </row>
-    <row r="127" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="6:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F127" s="34"/>
     </row>
   </sheetData>
@@ -5525,9 +5655,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A794A0B0-676E-447A-9608-121CAE2D9E27}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -5535,7 +5665,7 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>739</v>
       </c>
@@ -5555,7 +5685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>741</v>
       </c>
@@ -5575,7 +5705,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="128.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>741</v>
       </c>
@@ -5595,7 +5725,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>741</v>
       </c>
@@ -5615,7 +5745,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>741</v>
       </c>
@@ -5635,7 +5765,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="228" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>742</v>
       </c>
@@ -5655,7 +5785,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="288" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>742</v>
       </c>
@@ -5675,7 +5805,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>742</v>
       </c>
@@ -5695,7 +5825,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>743</v>
       </c>
@@ -5715,7 +5845,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>743</v>
       </c>
@@ -5735,7 +5865,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>742</v>
       </c>
@@ -5755,7 +5885,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>742</v>
       </c>
@@ -5775,7 +5905,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>744</v>
       </c>
@@ -5795,7 +5925,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="199.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>744</v>
       </c>
@@ -5815,7 +5945,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="213.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="216" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>743</v>
       </c>
@@ -5835,7 +5965,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="213.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="216" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>743</v>
       </c>
@@ -5855,7 +5985,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>745</v>
       </c>
@@ -5875,7 +6005,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="313.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>745</v>
       </c>
@@ -5895,7 +6025,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="185.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>741</v>
       </c>
@@ -5915,7 +6045,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="185.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>741</v>
       </c>
@@ -5935,7 +6065,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="185.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>744</v>
       </c>
@@ -5955,7 +6085,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="185.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>744</v>
       </c>
@@ -5975,7 +6105,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="156.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>744</v>
       </c>
@@ -5995,7 +6125,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="156.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>744</v>
       </c>
@@ -6015,7 +6145,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="213.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="216" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>743</v>
       </c>
@@ -6035,7 +6165,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="213.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="216" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>743</v>
       </c>
@@ -6055,7 +6185,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>742</v>
       </c>
@@ -6075,7 +6205,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="242.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>742</v>
       </c>
@@ -6095,7 +6225,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="142.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>744</v>
       </c>
@@ -6135,15 +6265,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DA5B44-931D-410B-A507-D21C90CF9E0A}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="2" max="3" width="34.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
         <v>641</v>
       </c>
@@ -6163,7 +6293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6178,7 +6308,7 @@
       </c>
       <c r="E2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -6193,7 +6323,7 @@
       </c>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -6208,7 +6338,7 @@
       </c>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
@@ -6223,7 +6353,7 @@
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6238,7 +6368,7 @@
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6253,7 +6383,7 @@
       </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6268,7 +6398,7 @@
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -6283,7 +6413,7 @@
       </c>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0</v>
       </c>
@@ -6298,7 +6428,7 @@
       </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6313,7 +6443,7 @@
       </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6328,7 +6458,7 @@
       </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6343,7 +6473,7 @@
       </c>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>3</v>
       </c>
@@ -6358,7 +6488,7 @@
       </c>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0</v>
       </c>
@@ -6373,7 +6503,7 @@
       </c>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -6388,7 +6518,7 @@
       </c>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -6403,7 +6533,7 @@
       </c>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -6418,7 +6548,7 @@
       </c>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -6433,7 +6563,7 @@
       </c>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -6448,7 +6578,7 @@
       </c>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:5" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -6463,7 +6593,7 @@
       </c>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:5" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1</v>
       </c>
@@ -6478,7 +6608,7 @@
       </c>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -6493,7 +6623,7 @@
       </c>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2</v>
       </c>
@@ -6508,7 +6638,7 @@
       </c>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -6523,7 +6653,7 @@
       </c>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2</v>
       </c>
@@ -6538,7 +6668,7 @@
       </c>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -6553,7 +6683,7 @@
       </c>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
@@ -6568,7 +6698,7 @@
       </c>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
@@ -6583,7 +6713,7 @@
       </c>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6598,7 +6728,7 @@
       </c>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="69" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6613,7 +6743,7 @@
       </c>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2</v>
       </c>
@@ -6628,7 +6758,7 @@
       </c>
       <c r="E32" s="6"/>
     </row>
-    <row r="33" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2</v>
       </c>
@@ -6643,7 +6773,7 @@
       </c>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2</v>
       </c>
@@ -6658,7 +6788,7 @@
       </c>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="69" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6673,7 +6803,7 @@
       </c>
       <c r="E35" s="6"/>
     </row>
-    <row r="36" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6688,7 +6818,7 @@
       </c>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2</v>
       </c>
@@ -6703,7 +6833,7 @@
       </c>
       <c r="E37" s="6"/>
     </row>
-    <row r="38" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="69" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -6718,7 +6848,7 @@
       </c>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6733,7 +6863,7 @@
       </c>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="69" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2</v>
       </c>
@@ -6748,7 +6878,7 @@
       </c>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6763,7 +6893,7 @@
       </c>
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:6" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6778,7 +6908,7 @@
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6793,7 +6923,7 @@
       </c>
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3</v>
       </c>
@@ -6808,7 +6938,7 @@
       </c>
       <c r="E44" s="6"/>
     </row>
-    <row r="45" spans="1:6" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -6823,42 +6953,42 @@
       </c>
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
       <c r="D51" s="6"/>
@@ -6886,17 +7016,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45928C10-1DB7-4733-A9E7-F209E2FA21CC}">
   <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="65.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.44140625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="59.42578125" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" customWidth="1"/>
+    <col min="5" max="5" width="59.44140625" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="48" t="s">
         <v>640</v>
       </c>
@@ -6916,7 +7046,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A2" s="41">
         <v>0</v>
       </c>
@@ -6936,7 +7066,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A3" s="41">
         <v>0</v>
       </c>
@@ -6956,7 +7086,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A4" s="41">
         <v>0</v>
       </c>
@@ -6976,7 +7106,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>0</v>
       </c>
@@ -6996,7 +7126,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A6" s="41">
         <v>0</v>
       </c>
@@ -7016,7 +7146,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>1</v>
       </c>
@@ -7036,7 +7166,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>1</v>
       </c>
@@ -7056,7 +7186,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A9" s="41">
         <v>1</v>
       </c>
@@ -7076,7 +7206,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="299.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="296.39999999999998" x14ac:dyDescent="0.3">
       <c r="A10" s="41">
         <v>1</v>
       </c>
@@ -7096,7 +7226,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <v>1</v>
       </c>
@@ -7116,7 +7246,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A12" s="41">
         <v>2</v>
       </c>
@@ -7136,7 +7266,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2</v>
       </c>
@@ -7156,7 +7286,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2</v>
       </c>
@@ -7176,7 +7306,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2</v>
       </c>
@@ -7196,7 +7326,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2</v>
       </c>
@@ -7216,7 +7346,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2</v>
       </c>
@@ -7236,7 +7366,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>3</v>
       </c>
@@ -7256,7 +7386,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>3</v>
       </c>
@@ -7276,7 +7406,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>3</v>
       </c>
@@ -7296,7 +7426,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="B21" s="43" t="s">
         <v>844</v>
       </c>
@@ -7309,121 +7439,121 @@
       <c r="E21" s="46"/>
       <c r="F21" s="46"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E22" s="46"/>
       <c r="F22" s="46"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E23" s="46"/>
       <c r="F23" s="41"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E26" s="46"/>
       <c r="F26" s="46"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E27" s="46"/>
       <c r="F27" s="46"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E28" s="46"/>
       <c r="F28" s="46"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E29" s="46"/>
       <c r="F29" s="46"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E30" s="46"/>
       <c r="F30" s="46"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E31" s="46"/>
       <c r="F31" s="46"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E32" s="46"/>
       <c r="F32" s="46"/>
     </row>
-    <row r="33" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E33" s="46"/>
       <c r="F33" s="46"/>
     </row>
-    <row r="34" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E34" s="46"/>
       <c r="F34" s="46"/>
     </row>
-    <row r="35" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E35" s="46"/>
       <c r="F35" s="46"/>
     </row>
-    <row r="36" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E36" s="46"/>
       <c r="F36" s="46"/>
     </row>
-    <row r="37" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E37" s="46"/>
       <c r="F37" s="46"/>
     </row>
-    <row r="38" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E38" s="46"/>
       <c r="F38" s="46"/>
     </row>
-    <row r="39" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E39" s="46"/>
       <c r="F39" s="46"/>
     </row>
-    <row r="40" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E40" s="46"/>
       <c r="F40" s="46"/>
     </row>
-    <row r="41" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E41" s="46"/>
       <c r="F41" s="46"/>
     </row>
-    <row r="42" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E42" s="46"/>
       <c r="F42" s="47"/>
     </row>
-    <row r="43" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E43" s="46"/>
       <c r="F43" s="42"/>
     </row>
-    <row r="44" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E44" s="46"/>
       <c r="F44" s="43"/>
     </row>
-    <row r="45" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E45" s="46"/>
       <c r="F45" s="44"/>
     </row>
-    <row r="46" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E46" s="46"/>
     </row>
-    <row r="47" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E47" s="46"/>
     </row>
-    <row r="48" spans="5:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E48" s="46"/>
     </row>
-    <row r="49" spans="5:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E49" s="46"/>
     </row>
-    <row r="50" spans="5:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E50" s="46"/>
     </row>
-    <row r="51" spans="5:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E51" s="46"/>
     </row>
-    <row r="52" spans="5:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E52" s="47"/>
     </row>
   </sheetData>
@@ -7434,17 +7564,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F83770C-ED8C-4CE7-AFA3-C3BD2CE4A9F0}">
   <dimension ref="A1:I83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="65.42578125" customWidth="1"/>
-    <col min="4" max="4" width="54.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="61.7109375" customWidth="1"/>
-    <col min="7" max="8" width="54.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="65.44140625" customWidth="1"/>
+    <col min="4" max="4" width="54.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="6" max="6" width="61.6640625" customWidth="1"/>
+    <col min="7" max="8" width="54.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>641</v>
       </c>
@@ -7470,7 +7600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7497,7 +7627,7 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -7521,7 +7651,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -7547,7 +7677,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
@@ -7573,7 +7703,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -7599,7 +7729,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
@@ -7625,7 +7755,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -7651,7 +7781,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0</v>
       </c>
@@ -7678,7 +7808,7 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -7704,7 +7834,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -7730,7 +7860,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -7756,7 +7886,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -7782,7 +7912,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -7808,7 +7938,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -7834,7 +7964,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -7860,7 +7990,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7886,7 +8016,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7912,7 +8042,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7938,7 +8068,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7964,7 +8094,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7990,7 +8120,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8016,7 +8146,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>3</v>
       </c>
@@ -8042,7 +8172,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8068,7 +8198,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8094,7 +8224,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8120,7 +8250,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8146,7 +8276,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8172,7 +8302,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>4</v>
       </c>
@@ -8198,7 +8328,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>4</v>
       </c>
@@ -8224,7 +8354,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>4</v>
       </c>
@@ -8250,7 +8380,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>4</v>
       </c>
@@ -8276,7 +8406,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>4</v>
       </c>
@@ -8302,7 +8432,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>4</v>
       </c>
@@ -8328,7 +8458,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>4</v>
       </c>
@@ -8354,7 +8484,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>4</v>
       </c>
@@ -8380,7 +8510,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>4</v>
       </c>
@@ -8406,7 +8536,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0</v>
       </c>
@@ -8432,7 +8562,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0</v>
       </c>
@@ -8458,7 +8588,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0</v>
       </c>
@@ -8484,7 +8614,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0</v>
       </c>
@@ -8510,7 +8640,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0</v>
       </c>
@@ -8536,7 +8666,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0</v>
       </c>
@@ -8562,7 +8692,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0</v>
       </c>
@@ -8588,7 +8718,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0</v>
       </c>
@@ -8614,7 +8744,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1</v>
       </c>
@@ -8640,7 +8770,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1</v>
       </c>
@@ -8666,7 +8796,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1</v>
       </c>
@@ -8692,7 +8822,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1</v>
       </c>
@@ -8718,7 +8848,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1</v>
       </c>
@@ -8744,7 +8874,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1</v>
       </c>
@@ -8770,7 +8900,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1</v>
       </c>
@@ -8796,7 +8926,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -8822,7 +8952,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1</v>
       </c>
@@ -8848,7 +8978,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2</v>
       </c>
@@ -8874,7 +9004,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2</v>
       </c>
@@ -8900,7 +9030,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2</v>
       </c>
@@ -8926,7 +9056,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2</v>
       </c>
@@ -8952,7 +9082,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2</v>
       </c>
@@ -8978,7 +9108,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2</v>
       </c>
@@ -9004,7 +9134,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="81" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2</v>
       </c>
@@ -9030,7 +9160,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>3</v>
       </c>
@@ -9056,7 +9186,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>3</v>
       </c>
@@ -9082,7 +9212,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>3</v>
       </c>
@@ -9108,7 +9238,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>3</v>
       </c>
@@ -9134,7 +9264,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>4</v>
       </c>
@@ -9160,7 +9290,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>4</v>
       </c>
@@ -9186,7 +9316,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>4</v>
       </c>
@@ -9212,7 +9342,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>4</v>
       </c>
@@ -9238,7 +9368,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>4</v>
       </c>
@@ -9264,7 +9394,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>4</v>
       </c>
@@ -9290,7 +9420,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>5</v>
       </c>
@@ -9316,7 +9446,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>5</v>
       </c>
@@ -9342,7 +9472,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>5</v>
       </c>
@@ -9368,7 +9498,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>5</v>
       </c>
@@ -9394,7 +9524,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>5</v>
       </c>
@@ -9420,7 +9550,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>5</v>
       </c>
@@ -9446,7 +9576,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>6</v>
       </c>
@@ -9472,7 +9602,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>6</v>
       </c>
@@ -9498,7 +9628,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>6</v>
       </c>
@@ -9524,7 +9654,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>6</v>
       </c>
@@ -9550,7 +9680,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>6</v>
       </c>
@@ -9576,7 +9706,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>6</v>
       </c>
@@ -9623,15 +9753,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE259F4-0938-4BD0-AA49-7D4BC9B2AEA8}">
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="29" defaultRowHeight="201.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="29" defaultRowHeight="201.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" customWidth="1"/>
-    <col min="2" max="2" width="54.85546875" customWidth="1"/>
-    <col min="3" max="3" width="56.85546875" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="54.88671875" customWidth="1"/>
+    <col min="3" max="3" width="56.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>640</v>
       </c>
@@ -9651,7 +9781,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50">
         <v>0</v>
       </c>
@@ -9669,7 +9799,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>0</v>
       </c>
@@ -9687,7 +9817,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="116.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="50">
         <v>0</v>
       </c>
@@ -9705,7 +9835,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="50">
         <v>0</v>
       </c>
@@ -9723,7 +9853,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50">
         <v>1</v>
       </c>
@@ -9741,7 +9871,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="158.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="158.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="50">
         <v>1</v>
       </c>
@@ -9759,7 +9889,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="131.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50">
         <v>1</v>
       </c>
@@ -9777,7 +9907,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50">
         <v>1</v>
       </c>
@@ -9795,7 +9925,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>2</v>
       </c>
@@ -9815,7 +9945,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>2</v>
       </c>
@@ -9835,7 +9965,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="50">
         <v>2</v>
       </c>
@@ -9853,7 +9983,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="50">
         <v>2</v>
       </c>
@@ -9871,7 +10001,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="50">
         <v>2</v>
       </c>
@@ -9889,7 +10019,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="50">
         <v>2</v>
       </c>
@@ -9907,7 +10037,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="50">
         <v>3</v>
       </c>
@@ -9925,7 +10055,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>3</v>
       </c>
@@ -9943,7 +10073,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="50">
         <v>3</v>
       </c>
@@ -9961,7 +10091,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="50">
         <v>3</v>
       </c>
@@ -9979,7 +10109,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50">
         <v>4</v>
       </c>
@@ -9997,7 +10127,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50">
         <v>5</v>
       </c>
@@ -10015,7 +10145,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="50">
         <v>5</v>
       </c>
@@ -10033,7 +10163,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="201.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="51"/>
       <c r="B23" s="52"/>
       <c r="C23" s="7"/>
